--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123190386</v>
+        <v>123190588</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576336</v>
+        <v>576369</v>
       </c>
       <c r="R2" t="n">
-        <v>7059742</v>
+        <v>7059717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123190061</v>
+        <v>123188773</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576304</v>
+        <v>576394</v>
       </c>
       <c r="R3" t="n">
-        <v>7059697</v>
+        <v>7059632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123188791</v>
+        <v>123190386</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576384</v>
+        <v>576336</v>
       </c>
       <c r="R4" t="n">
-        <v>7059635</v>
+        <v>7059742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123189740</v>
+        <v>123188745</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576318</v>
+        <v>576416</v>
       </c>
       <c r="R5" t="n">
-        <v>7059620</v>
+        <v>7059643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123189834</v>
+        <v>123190577</v>
       </c>
       <c r="B6" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1145,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576317</v>
+        <v>576361</v>
       </c>
       <c r="R6" t="n">
-        <v>7059601</v>
+        <v>7059740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123188866</v>
+        <v>123190117</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576373</v>
+        <v>576296</v>
       </c>
       <c r="R7" t="n">
-        <v>7059626</v>
+        <v>7059711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123190373</v>
+        <v>123190061</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,43 +1384,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576354</v>
+        <v>576304</v>
       </c>
       <c r="R8" t="n">
-        <v>7059721</v>
+        <v>7059697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123189675</v>
+        <v>123188791</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1500,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576349</v>
+        <v>576384</v>
       </c>
       <c r="R9" t="n">
-        <v>7059624</v>
+        <v>7059635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188773</v>
+        <v>123190332</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576394</v>
+        <v>576339</v>
       </c>
       <c r="R10" t="n">
-        <v>7059632</v>
+        <v>7059723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1686,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,22 +1706,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123190117</v>
+        <v>123189740</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576296</v>
+        <v>576318</v>
       </c>
       <c r="R11" t="n">
-        <v>7059711</v>
+        <v>7059620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,12 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123188745</v>
+        <v>123188866</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,43 +1842,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576416</v>
+        <v>576373</v>
       </c>
       <c r="R12" t="n">
-        <v>7059643</v>
+        <v>7059626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123190577</v>
+        <v>123189834</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,43 +1954,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576361</v>
+        <v>576317</v>
       </c>
       <c r="R13" t="n">
-        <v>7059740</v>
+        <v>7059601</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190332</v>
+        <v>123190373</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,31 +2066,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576339</v>
+        <v>576354</v>
       </c>
       <c r="R14" t="n">
-        <v>7059723</v>
+        <v>7059721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,12 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,19 +2159,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123190588</v>
+        <v>123189675</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576369</v>
+        <v>576349</v>
       </c>
       <c r="R15" t="n">
-        <v>7059717</v>
+        <v>7059624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123190588</v>
+        <v>123189740</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576369</v>
+        <v>576318</v>
       </c>
       <c r="R2" t="n">
-        <v>7059717</v>
+        <v>7059620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188773</v>
+        <v>123190386</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576394</v>
+        <v>576336</v>
       </c>
       <c r="R3" t="n">
-        <v>7059632</v>
+        <v>7059742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123190386</v>
+        <v>123190332</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +916,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576336</v>
+        <v>576339</v>
       </c>
       <c r="R4" t="n">
-        <v>7059742</v>
+        <v>7059723</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123188745</v>
+        <v>123188773</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1038,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576416</v>
+        <v>576394</v>
       </c>
       <c r="R5" t="n">
-        <v>7059643</v>
+        <v>7059632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190577</v>
+        <v>123190061</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576361</v>
+        <v>576304</v>
       </c>
       <c r="R6" t="n">
-        <v>7059740</v>
+        <v>7059697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123190117</v>
+        <v>123190373</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,31 +1262,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576296</v>
+        <v>576354</v>
       </c>
       <c r="R7" t="n">
-        <v>7059711</v>
+        <v>7059721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123190061</v>
+        <v>123190117</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1383,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576304</v>
+        <v>576296</v>
       </c>
       <c r="R8" t="n">
-        <v>7059697</v>
+        <v>7059711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123188791</v>
+        <v>123189834</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>97319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,25 +1501,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576384</v>
+        <v>576317</v>
       </c>
       <c r="R9" t="n">
-        <v>7059635</v>
+        <v>7059601</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123190332</v>
+        <v>123188791</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,39 +1617,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576339</v>
+        <v>576384</v>
       </c>
       <c r="R10" t="n">
-        <v>7059723</v>
+        <v>7059635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,12 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189740</v>
+        <v>123189675</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576318</v>
+        <v>576349</v>
       </c>
       <c r="R11" t="n">
-        <v>7059620</v>
+        <v>7059624</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1942,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123189834</v>
+        <v>123190577</v>
       </c>
       <c r="B13" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,38 +1949,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576317</v>
+        <v>576361</v>
       </c>
       <c r="R13" t="n">
-        <v>7059601</v>
+        <v>7059740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190373</v>
+        <v>123190588</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,43 +2066,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576354</v>
+        <v>576369</v>
       </c>
       <c r="R14" t="n">
-        <v>7059721</v>
+        <v>7059717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,22 +2154,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123189675</v>
+        <v>123188745</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,38 +2178,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576349</v>
+        <v>576416</v>
       </c>
       <c r="R15" t="n">
-        <v>7059624</v>
+        <v>7059643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123189740</v>
+        <v>123190373</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576318</v>
+        <v>576354</v>
       </c>
       <c r="R2" t="n">
-        <v>7059620</v>
+        <v>7059721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123190386</v>
+        <v>123188866</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576336</v>
+        <v>576373</v>
       </c>
       <c r="R3" t="n">
-        <v>7059742</v>
+        <v>7059626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123190332</v>
+        <v>123188791</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576339</v>
+        <v>576384</v>
       </c>
       <c r="R4" t="n">
-        <v>7059723</v>
+        <v>7059635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123188773</v>
+        <v>123190577</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576394</v>
+        <v>576361</v>
       </c>
       <c r="R5" t="n">
-        <v>7059632</v>
+        <v>7059740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190061</v>
+        <v>123190332</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576304</v>
+        <v>576339</v>
       </c>
       <c r="R6" t="n">
-        <v>7059697</v>
+        <v>7059723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123190373</v>
+        <v>123188773</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,43 +1267,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576354</v>
+        <v>576394</v>
       </c>
       <c r="R7" t="n">
-        <v>7059721</v>
+        <v>7059632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123190117</v>
+        <v>123189675</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576296</v>
+        <v>576349</v>
       </c>
       <c r="R8" t="n">
-        <v>7059711</v>
+        <v>7059624</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123189834</v>
+        <v>123190588</v>
       </c>
       <c r="B9" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576317</v>
+        <v>576369</v>
       </c>
       <c r="R9" t="n">
-        <v>7059601</v>
+        <v>7059717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1579,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188791</v>
+        <v>123190117</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576384</v>
+        <v>576296</v>
       </c>
       <c r="R10" t="n">
-        <v>7059635</v>
+        <v>7059711</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189675</v>
+        <v>123190386</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,38 +1725,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576349</v>
+        <v>576336</v>
       </c>
       <c r="R11" t="n">
-        <v>7059624</v>
+        <v>7059742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123188866</v>
+        <v>123189740</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1865,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576373</v>
+        <v>576318</v>
       </c>
       <c r="R12" t="n">
-        <v>7059626</v>
+        <v>7059620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123190577</v>
+        <v>123188745</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,31 +1954,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1982,10 +1987,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576361</v>
+        <v>576416</v>
       </c>
       <c r="R13" t="n">
-        <v>7059740</v>
+        <v>7059643</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,22 +2047,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190588</v>
+        <v>123190061</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,21 +2075,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576369</v>
+        <v>576304</v>
       </c>
       <c r="R14" t="n">
-        <v>7059717</v>
+        <v>7059697</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123188745</v>
+        <v>123189834</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>97319</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,39 +2187,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576416</v>
+        <v>576317</v>
       </c>
       <c r="R15" t="n">
-        <v>7059643</v>
+        <v>7059601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,12 +2271,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123190373</v>
+        <v>123188773</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576354</v>
+        <v>576394</v>
       </c>
       <c r="R2" t="n">
-        <v>7059721</v>
+        <v>7059632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188866</v>
+        <v>123190332</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576373</v>
+        <v>576339</v>
       </c>
       <c r="R3" t="n">
-        <v>7059626</v>
+        <v>7059723</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123188791</v>
+        <v>123189675</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576384</v>
+        <v>576349</v>
       </c>
       <c r="R4" t="n">
-        <v>7059635</v>
+        <v>7059624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123190577</v>
+        <v>123190386</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,31 +1033,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576361</v>
+        <v>576336</v>
       </c>
       <c r="R5" t="n">
-        <v>7059740</v>
+        <v>7059742</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190332</v>
+        <v>123190061</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576339</v>
+        <v>576304</v>
       </c>
       <c r="R6" t="n">
-        <v>7059723</v>
+        <v>7059697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123188773</v>
+        <v>123189834</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>97322</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576394</v>
+        <v>576317</v>
       </c>
       <c r="R7" t="n">
-        <v>7059632</v>
+        <v>7059601</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123189675</v>
+        <v>123190577</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1378,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576349</v>
+        <v>576361</v>
       </c>
       <c r="R8" t="n">
-        <v>7059624</v>
+        <v>7059740</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123190588</v>
+        <v>123190373</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,38 +1491,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576369</v>
+        <v>576354</v>
       </c>
       <c r="R9" t="n">
-        <v>7059717</v>
+        <v>7059721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123190117</v>
+        <v>123188866</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,39 +1612,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576296</v>
+        <v>576373</v>
       </c>
       <c r="R10" t="n">
-        <v>7059711</v>
+        <v>7059626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123190386</v>
+        <v>123190117</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,31 +1720,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576336</v>
+        <v>576296</v>
       </c>
       <c r="R11" t="n">
-        <v>7059742</v>
+        <v>7059711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1798,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123189740</v>
+        <v>123188745</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>56691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1842,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576318</v>
+        <v>576416</v>
       </c>
       <c r="R12" t="n">
-        <v>7059620</v>
+        <v>7059643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123188745</v>
+        <v>123188791</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>79850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,43 +1959,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576416</v>
+        <v>576384</v>
       </c>
       <c r="R13" t="n">
-        <v>7059643</v>
+        <v>7059635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190061</v>
+        <v>123189740</v>
       </c>
       <c r="B14" t="n">
-        <v>78503</v>
+        <v>79850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576304</v>
+        <v>576318</v>
       </c>
       <c r="R14" t="n">
-        <v>7059697</v>
+        <v>7059620</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123189834</v>
+        <v>123190588</v>
       </c>
       <c r="B15" t="n">
-        <v>97319</v>
+        <v>78769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,25 +2183,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576317</v>
+        <v>576369</v>
       </c>
       <c r="R15" t="n">
-        <v>7059601</v>
+        <v>7059717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,12 +2271,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123188773</v>
+        <v>123188866</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576394</v>
+        <v>576373</v>
       </c>
       <c r="R2" t="n">
-        <v>7059632</v>
+        <v>7059626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123190332</v>
+        <v>123188773</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576339</v>
+        <v>576394</v>
       </c>
       <c r="R3" t="n">
-        <v>7059723</v>
+        <v>7059632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -912,7 +902,7 @@
         <v>123189675</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190061</v>
+        <v>123190332</v>
       </c>
       <c r="B6" t="n">
-        <v>78506</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576304</v>
+        <v>576339</v>
       </c>
       <c r="R6" t="n">
-        <v>7059697</v>
+        <v>7059723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1253,7 @@
         <v>123189834</v>
       </c>
       <c r="B7" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123190577</v>
+        <v>123190588</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,39 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576361</v>
+        <v>576369</v>
       </c>
       <c r="R8" t="n">
-        <v>7059740</v>
+        <v>7059717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1462,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1596,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188866</v>
+        <v>123188745</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1603,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576373</v>
+        <v>576416</v>
       </c>
       <c r="R10" t="n">
-        <v>7059626</v>
+        <v>7059643</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,12 +1696,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123188745</v>
+        <v>123190061</v>
       </c>
       <c r="B12" t="n">
-        <v>56691</v>
+        <v>78508</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,43 +1842,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576416</v>
+        <v>576304</v>
       </c>
       <c r="R12" t="n">
-        <v>7059643</v>
+        <v>7059697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123188791</v>
+        <v>123190577</v>
       </c>
       <c r="B13" t="n">
-        <v>79850</v>
+        <v>57497</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,34 +1958,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576384</v>
+        <v>576361</v>
       </c>
       <c r="R13" t="n">
-        <v>7059635</v>
+        <v>7059740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,22 +2047,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123189740</v>
+        <v>123188791</v>
       </c>
       <c r="B14" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576318</v>
+        <v>576384</v>
       </c>
       <c r="R14" t="n">
-        <v>7059620</v>
+        <v>7059635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,10 +2171,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123190588</v>
+        <v>123189740</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,21 +2187,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576369</v>
+        <v>576318</v>
       </c>
       <c r="R15" t="n">
-        <v>7059717</v>
+        <v>7059620</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123189834</v>
+        <v>123190588</v>
       </c>
       <c r="B7" t="n">
-        <v>97324</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1262,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576317</v>
+        <v>576369</v>
       </c>
       <c r="R7" t="n">
-        <v>7059601</v>
+        <v>7059717</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123190588</v>
+        <v>123189834</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>97324</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576369</v>
+        <v>576317</v>
       </c>
       <c r="R8" t="n">
-        <v>7059717</v>
+        <v>7059601</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,12 +1462,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123188866</v>
+        <v>123190588</v>
       </c>
       <c r="B2" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576373</v>
+        <v>576369</v>
       </c>
       <c r="R2" t="n">
-        <v>7059626</v>
+        <v>7059717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188773</v>
+        <v>123190061</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576394</v>
+        <v>576304</v>
       </c>
       <c r="R3" t="n">
-        <v>7059632</v>
+        <v>7059697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123189675</v>
+        <v>123188866</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576349</v>
+        <v>576373</v>
       </c>
       <c r="R4" t="n">
-        <v>7059624</v>
+        <v>7059626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123190386</v>
+        <v>123188745</v>
       </c>
       <c r="B5" t="n">
         <v>56691</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576336</v>
+        <v>576416</v>
       </c>
       <c r="R5" t="n">
-        <v>7059742</v>
+        <v>7059643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190332</v>
+        <v>123190373</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>56691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,31 +1140,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576339</v>
+        <v>576354</v>
       </c>
       <c r="R6" t="n">
-        <v>7059723</v>
+        <v>7059721</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123190588</v>
+        <v>123189740</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576369</v>
+        <v>576318</v>
       </c>
       <c r="R7" t="n">
-        <v>7059717</v>
+        <v>7059620</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123189834</v>
+        <v>123188791</v>
       </c>
       <c r="B8" t="n">
-        <v>97324</v>
+        <v>79853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1369,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576317</v>
+        <v>576384</v>
       </c>
       <c r="R8" t="n">
-        <v>7059601</v>
+        <v>7059635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1457,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123190373</v>
+        <v>123189675</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,43 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576354</v>
+        <v>576349</v>
       </c>
       <c r="R9" t="n">
-        <v>7059721</v>
+        <v>7059624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188745</v>
+        <v>123190332</v>
       </c>
       <c r="B10" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,31 +1593,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1636,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576416</v>
+        <v>576339</v>
       </c>
       <c r="R10" t="n">
-        <v>7059643</v>
+        <v>7059723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1671,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123190117</v>
+        <v>123188773</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,39 +1719,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576296</v>
+        <v>576394</v>
       </c>
       <c r="R11" t="n">
-        <v>7059711</v>
+        <v>7059632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,12 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,22 +1803,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123190061</v>
+        <v>123190386</v>
       </c>
       <c r="B12" t="n">
-        <v>78508</v>
+        <v>56691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,38 +1827,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576304</v>
+        <v>576336</v>
       </c>
       <c r="R12" t="n">
-        <v>7059697</v>
+        <v>7059742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2059,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123188791</v>
+        <v>123189834</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>97330</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,25 +2061,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576384</v>
+        <v>576317</v>
       </c>
       <c r="R14" t="n">
-        <v>7059635</v>
+        <v>7059601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,22 +2149,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123189740</v>
+        <v>123190117</v>
       </c>
       <c r="B15" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,34 +2177,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576318</v>
+        <v>576296</v>
       </c>
       <c r="R15" t="n">
-        <v>7059620</v>
+        <v>7059711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2251,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123190577</v>
+        <v>123190373</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576361</v>
+        <v>576354</v>
       </c>
       <c r="R2" t="n">
-        <v>7059740</v>
+        <v>7059721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123189675</v>
+        <v>123190386</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576349</v>
+        <v>576336</v>
       </c>
       <c r="R3" t="n">
-        <v>7059624</v>
+        <v>7059742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123188866</v>
+        <v>123190332</v>
       </c>
       <c r="B4" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576373</v>
+        <v>576339</v>
       </c>
       <c r="R4" t="n">
-        <v>7059626</v>
+        <v>7059723</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123188791</v>
+        <v>123190588</v>
       </c>
       <c r="B5" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576384</v>
+        <v>576369</v>
       </c>
       <c r="R5" t="n">
-        <v>7059635</v>
+        <v>7059717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190332</v>
+        <v>123189834</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>97350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,43 +1155,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576339</v>
+        <v>576317</v>
       </c>
       <c r="R6" t="n">
-        <v>7059723</v>
+        <v>7059601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123190061</v>
+        <v>123188791</v>
       </c>
       <c r="B7" t="n">
-        <v>78512</v>
+        <v>79862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576304</v>
+        <v>576384</v>
       </c>
       <c r="R7" t="n">
-        <v>7059697</v>
+        <v>7059635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123190373</v>
+        <v>123189740</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>79862</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,43 +1379,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576354</v>
+        <v>576318</v>
       </c>
       <c r="R8" t="n">
-        <v>7059721</v>
+        <v>7059620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123189834</v>
+        <v>123188745</v>
       </c>
       <c r="B9" t="n">
-        <v>97333</v>
+        <v>56697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576317</v>
+        <v>576416</v>
       </c>
       <c r="R9" t="n">
-        <v>7059601</v>
+        <v>7059643</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188773</v>
+        <v>123188866</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1612,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576394</v>
+        <v>576373</v>
       </c>
       <c r="R10" t="n">
-        <v>7059632</v>
+        <v>7059626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189740</v>
+        <v>123189675</v>
       </c>
       <c r="B11" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576318</v>
+        <v>576349</v>
       </c>
       <c r="R11" t="n">
-        <v>7059620</v>
+        <v>7059624</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123190588</v>
+        <v>123190061</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>78518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576369</v>
+        <v>576304</v>
       </c>
       <c r="R12" t="n">
-        <v>7059717</v>
+        <v>7059697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123190117</v>
+        <v>123188773</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,39 +1948,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576296</v>
+        <v>576394</v>
       </c>
       <c r="R13" t="n">
-        <v>7059711</v>
+        <v>7059632</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,12 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,22 +2032,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190386</v>
+        <v>123190117</v>
       </c>
       <c r="B14" t="n">
-        <v>56691</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,31 +2056,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576336</v>
+        <v>576296</v>
       </c>
       <c r="R14" t="n">
-        <v>7059742</v>
+        <v>7059711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2134,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123188745</v>
+        <v>123190577</v>
       </c>
       <c r="B15" t="n">
-        <v>56691</v>
+        <v>57503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,31 +2178,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576416</v>
+        <v>576361</v>
       </c>
       <c r="R15" t="n">
-        <v>7059643</v>
+        <v>7059740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,12 +2271,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123188745</v>
+        <v>123189675</v>
       </c>
       <c r="B9" t="n">
-        <v>56697</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,43 +1491,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576416</v>
+        <v>576349</v>
       </c>
       <c r="R9" t="n">
-        <v>7059643</v>
+        <v>7059624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188866</v>
+        <v>123188745</v>
       </c>
       <c r="B10" t="n">
-        <v>79862</v>
+        <v>56697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1603,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576373</v>
+        <v>576416</v>
       </c>
       <c r="R10" t="n">
-        <v>7059626</v>
+        <v>7059643</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189675</v>
+        <v>123188866</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>79862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576349</v>
+        <v>576373</v>
       </c>
       <c r="R11" t="n">
-        <v>7059624</v>
+        <v>7059626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,12 +1808,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123190373</v>
+        <v>123190386</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576354</v>
+        <v>576336</v>
       </c>
       <c r="R2" t="n">
-        <v>7059721</v>
+        <v>7059742</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123190386</v>
+        <v>123188866</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>79867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576336</v>
+        <v>576373</v>
       </c>
       <c r="R3" t="n">
-        <v>7059742</v>
+        <v>7059626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123190332</v>
+        <v>123190061</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>78523</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576339</v>
+        <v>576304</v>
       </c>
       <c r="R4" t="n">
-        <v>7059723</v>
+        <v>7059697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123190588</v>
+        <v>123190332</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576369</v>
+        <v>576339</v>
       </c>
       <c r="R5" t="n">
-        <v>7059717</v>
+        <v>7059723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123189834</v>
+        <v>123190588</v>
       </c>
       <c r="B6" t="n">
-        <v>97350</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576317</v>
+        <v>576369</v>
       </c>
       <c r="R6" t="n">
-        <v>7059601</v>
+        <v>7059717</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123188791</v>
+        <v>123189675</v>
       </c>
       <c r="B7" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576384</v>
+        <v>576349</v>
       </c>
       <c r="R7" t="n">
-        <v>7059635</v>
+        <v>7059624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123189740</v>
+        <v>123188773</v>
       </c>
       <c r="B8" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576318</v>
+        <v>576394</v>
       </c>
       <c r="R8" t="n">
-        <v>7059620</v>
+        <v>7059632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1462,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123189675</v>
+        <v>123189834</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>97367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576349</v>
+        <v>576317</v>
       </c>
       <c r="R9" t="n">
-        <v>7059624</v>
+        <v>7059601</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188745</v>
+        <v>123188791</v>
       </c>
       <c r="B10" t="n">
-        <v>56697</v>
+        <v>79867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,43 +1598,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576416</v>
+        <v>576384</v>
       </c>
       <c r="R10" t="n">
-        <v>7059643</v>
+        <v>7059635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123188866</v>
+        <v>123189740</v>
       </c>
       <c r="B11" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576373</v>
+        <v>576318</v>
       </c>
       <c r="R11" t="n">
-        <v>7059626</v>
+        <v>7059620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,22 +1798,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123190061</v>
+        <v>123190117</v>
       </c>
       <c r="B12" t="n">
-        <v>78518</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576304</v>
+        <v>576296</v>
       </c>
       <c r="R12" t="n">
-        <v>7059697</v>
+        <v>7059711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1900,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123188773</v>
+        <v>123190373</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,38 +1944,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576394</v>
+        <v>576354</v>
       </c>
       <c r="R13" t="n">
-        <v>7059632</v>
+        <v>7059721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2049,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190117</v>
+        <v>123188745</v>
       </c>
       <c r="B14" t="n">
-        <v>57487</v>
+        <v>56700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,31 +2061,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2089,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576296</v>
+        <v>576416</v>
       </c>
       <c r="R14" t="n">
-        <v>7059711</v>
+        <v>7059643</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,12 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,7 +2169,7 @@
         <v>123190577</v>
       </c>
       <c r="B15" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123190386</v>
+        <v>123188773</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576336</v>
+        <v>576394</v>
       </c>
       <c r="R2" t="n">
-        <v>7059742</v>
+        <v>7059632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188866</v>
+        <v>123188745</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576373</v>
+        <v>576416</v>
       </c>
       <c r="R3" t="n">
-        <v>7059626</v>
+        <v>7059643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123190061</v>
+        <v>123189675</v>
       </c>
       <c r="B4" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576304</v>
+        <v>576349</v>
       </c>
       <c r="R4" t="n">
-        <v>7059697</v>
+        <v>7059624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123190332</v>
+        <v>123189834</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>97369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576339</v>
+        <v>576317</v>
       </c>
       <c r="R5" t="n">
-        <v>7059723</v>
+        <v>7059601</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190588</v>
+        <v>123190332</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576369</v>
+        <v>576339</v>
       </c>
       <c r="R6" t="n">
-        <v>7059717</v>
+        <v>7059723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123189675</v>
+        <v>123190577</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576349</v>
+        <v>576361</v>
       </c>
       <c r="R7" t="n">
-        <v>7059624</v>
+        <v>7059740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123188773</v>
+        <v>123189740</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576394</v>
+        <v>576318</v>
       </c>
       <c r="R8" t="n">
-        <v>7059632</v>
+        <v>7059620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123189834</v>
+        <v>123188866</v>
       </c>
       <c r="B9" t="n">
-        <v>97367</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1491,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576317</v>
+        <v>576373</v>
       </c>
       <c r="R9" t="n">
-        <v>7059601</v>
+        <v>7059626</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188791</v>
+        <v>123190588</v>
       </c>
       <c r="B10" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576384</v>
+        <v>576369</v>
       </c>
       <c r="R10" t="n">
-        <v>7059635</v>
+        <v>7059717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123189740</v>
+        <v>123190117</v>
       </c>
       <c r="B11" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1719,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576318</v>
+        <v>576296</v>
       </c>
       <c r="R11" t="n">
-        <v>7059620</v>
+        <v>7059711</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123190117</v>
+        <v>123190061</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>78525</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576296</v>
+        <v>576304</v>
       </c>
       <c r="R12" t="n">
-        <v>7059711</v>
+        <v>7059697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,12 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123190373</v>
+        <v>123188791</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,43 +1949,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576354</v>
+        <v>576384</v>
       </c>
       <c r="R13" t="n">
-        <v>7059721</v>
+        <v>7059635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,19 +2037,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123188745</v>
+        <v>123190373</v>
       </c>
       <c r="B14" t="n">
         <v>56700</v>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576416</v>
+        <v>576354</v>
       </c>
       <c r="R14" t="n">
-        <v>7059643</v>
+        <v>7059721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,22 +2154,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123190577</v>
+        <v>123190386</v>
       </c>
       <c r="B15" t="n">
-        <v>57506</v>
+        <v>56700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,31 +2178,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576361</v>
+        <v>576336</v>
       </c>
       <c r="R15" t="n">
-        <v>7059740</v>
+        <v>7059742</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,12 +2271,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123189834</v>
+        <v>123190332</v>
       </c>
       <c r="B5" t="n">
-        <v>97369</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576317</v>
+        <v>576339</v>
       </c>
       <c r="R5" t="n">
-        <v>7059601</v>
+        <v>7059723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190332</v>
+        <v>123189834</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>97369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,43 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576339</v>
+        <v>576317</v>
       </c>
       <c r="R6" t="n">
-        <v>7059723</v>
+        <v>7059601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123188791</v>
+        <v>123190373</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,38 +1949,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576384</v>
+        <v>576354</v>
       </c>
       <c r="R13" t="n">
-        <v>7059635</v>
+        <v>7059721</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,19 +2042,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190373</v>
+        <v>123190386</v>
       </c>
       <c r="B14" t="n">
         <v>56700</v>
@@ -2094,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576354</v>
+        <v>576336</v>
       </c>
       <c r="R14" t="n">
-        <v>7059721</v>
+        <v>7059742</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2134,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2144,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,22 +2159,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123190386</v>
+        <v>123188791</v>
       </c>
       <c r="B15" t="n">
-        <v>56700</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,43 +2183,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576336</v>
+        <v>576384</v>
       </c>
       <c r="R15" t="n">
-        <v>7059742</v>
+        <v>7059635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123190332</v>
+        <v>123189834</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>97369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576339</v>
+        <v>576317</v>
       </c>
       <c r="R5" t="n">
-        <v>7059723</v>
+        <v>7059601</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123189834</v>
+        <v>123190332</v>
       </c>
       <c r="B6" t="n">
-        <v>97369</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1140,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576317</v>
+        <v>576339</v>
       </c>
       <c r="R6" t="n">
-        <v>7059601</v>
+        <v>7059723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123188773</v>
+        <v>123190332</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576394</v>
+        <v>576339</v>
       </c>
       <c r="R2" t="n">
-        <v>7059632</v>
+        <v>7059723</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123188745</v>
+        <v>123190061</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576416</v>
+        <v>576304</v>
       </c>
       <c r="R3" t="n">
-        <v>7059643</v>
+        <v>7059697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123189675</v>
+        <v>123188866</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576349</v>
+        <v>576373</v>
       </c>
       <c r="R4" t="n">
-        <v>7059624</v>
+        <v>7059626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123189834</v>
+        <v>123190588</v>
       </c>
       <c r="B5" t="n">
-        <v>97369</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576317</v>
+        <v>576369</v>
       </c>
       <c r="R5" t="n">
-        <v>7059601</v>
+        <v>7059717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190332</v>
+        <v>123190577</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576339</v>
+        <v>576361</v>
       </c>
       <c r="R6" t="n">
-        <v>7059723</v>
+        <v>7059740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123190577</v>
+        <v>123189675</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576361</v>
+        <v>576349</v>
       </c>
       <c r="R7" t="n">
-        <v>7059740</v>
+        <v>7059624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123189740</v>
+        <v>123188745</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1374,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576318</v>
+        <v>576416</v>
       </c>
       <c r="R8" t="n">
-        <v>7059620</v>
+        <v>7059643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123188866</v>
+        <v>123189740</v>
       </c>
       <c r="B9" t="n">
         <v>79869</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576373</v>
+        <v>576318</v>
       </c>
       <c r="R9" t="n">
-        <v>7059626</v>
+        <v>7059620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,22 +1579,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123190588</v>
+        <v>123188791</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576369</v>
+        <v>576384</v>
       </c>
       <c r="R10" t="n">
-        <v>7059717</v>
+        <v>7059635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123190117</v>
+        <v>123190386</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,31 +1715,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576296</v>
+        <v>576336</v>
       </c>
       <c r="R11" t="n">
-        <v>7059711</v>
+        <v>7059742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123190061</v>
+        <v>123188773</v>
       </c>
       <c r="B12" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576304</v>
+        <v>576394</v>
       </c>
       <c r="R12" t="n">
-        <v>7059697</v>
+        <v>7059632</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123190373</v>
+        <v>123189834</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>96957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,39 +1948,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576354</v>
+        <v>576317</v>
       </c>
       <c r="R13" t="n">
-        <v>7059721</v>
+        <v>7059601</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123190386</v>
+        <v>123190373</v>
       </c>
       <c r="B14" t="n">
         <v>56700</v>
@@ -2099,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576336</v>
+        <v>576354</v>
       </c>
       <c r="R14" t="n">
-        <v>7059742</v>
+        <v>7059721</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,22 +2149,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123188791</v>
+        <v>123190117</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,34 +2177,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576384</v>
+        <v>576296</v>
       </c>
       <c r="R15" t="n">
-        <v>7059635</v>
+        <v>7059711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,7 +2251,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123190332</v>
+        <v>123188706</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576339</v>
+        <v>576451</v>
       </c>
       <c r="R2" t="n">
-        <v>7059723</v>
+        <v>7059679</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123190061</v>
+        <v>123188773</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576304</v>
+        <v>576394</v>
       </c>
       <c r="R3" t="n">
-        <v>7059697</v>
+        <v>7059632</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,49 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123188866</v>
+        <v>123189675</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576373</v>
+        <v>576349</v>
       </c>
       <c r="R4" t="n">
-        <v>7059626</v>
+        <v>7059624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1024,16 +999,11 @@
         <v>123190588</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1133,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123190577</v>
+        <v>123188791</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576361</v>
+        <v>576384</v>
       </c>
       <c r="R6" t="n">
-        <v>7059740</v>
+        <v>7059635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,27 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123189675</v>
+        <v>123188866</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576349</v>
+        <v>576373</v>
       </c>
       <c r="R7" t="n">
-        <v>7059624</v>
+        <v>7059626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,67 +1305,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123188745</v>
+        <v>123189740</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576416</v>
+        <v>576318</v>
       </c>
       <c r="R8" t="n">
-        <v>7059643</v>
+        <v>7059620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,50 +1424,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123189740</v>
+        <v>123190577</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576318</v>
+        <v>576361</v>
       </c>
       <c r="R9" t="n">
-        <v>7059620</v>
+        <v>7059740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,27 +1524,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123188791</v>
+        <v>123190117</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,34 +1547,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576384</v>
+        <v>576296</v>
       </c>
       <c r="R10" t="n">
-        <v>7059635</v>
+        <v>7059711</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1621,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,43 +1653,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123190386</v>
+        <v>123190332</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1748,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576336</v>
+        <v>576339</v>
       </c>
       <c r="R11" t="n">
-        <v>7059742</v>
+        <v>7059723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,15 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123188773</v>
+        <v>123190618</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,34 +1781,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576394</v>
+        <v>576378</v>
       </c>
       <c r="R12" t="n">
-        <v>7059632</v>
+        <v>7059748</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1855,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,15 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123189834</v>
+        <v>123188745</v>
       </c>
       <c r="B13" t="n">
-        <v>96957</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,34 +1898,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576317</v>
+        <v>576416</v>
       </c>
       <c r="R13" t="n">
-        <v>7059601</v>
+        <v>7059643</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,12 +1987,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2047,12 +2002,7 @@
         <v>123190373</v>
       </c>
       <c r="B14" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,43 +2111,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123190117</v>
+        <v>123190386</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2206,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576296</v>
+        <v>576336</v>
       </c>
       <c r="R15" t="n">
-        <v>7059711</v>
+        <v>7059742</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,12 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,6 +2220,220 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123189834</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>576317</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7059601</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123190061</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bodtjärnsbäcken, Bodtjärnsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>576304</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7059697</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12174-2025 artfynd.xlsx
+++ b/artfynd/A 12174-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188706</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188773</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123189675</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190588</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188791</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188866</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123189740</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190577</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190117</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190332</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190618</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123188745</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190373</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190386</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123189834</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,8 +2514,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123190061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>